--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104702_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104702_W28.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9506</v>
+        <v>8.424799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4323</v>
+        <v>5.5963</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5183</v>
+        <v>2.8285</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1964</v>
+        <v>6.2045</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1239</v>
+        <v>1.1339</v>
       </c>
       <c r="I2" t="n">
-        <v>5.0725</v>
+        <v>5.0706</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9426</v>
+        <v>4.9247</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9524</v>
+        <v>0.948</v>
       </c>
       <c r="L2" t="n">
-        <v>3.9902</v>
+        <v>3.9767</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2538</v>
+        <v>1.2798</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.155</v>
+        <v>-0.6886</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.378</v>
+        <v>-0.1886</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.777</v>
+        <v>-0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1256</v>
+        <v>3.6527</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5321</v>
+        <v>2.3818</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5936</v>
+        <v>1.2709</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3669</v>
+        <v>0.362</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5656</v>
+        <v>-1.5653</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9325</v>
+        <v>1.9273</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2294</v>
+        <v>1.2091</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4471</v>
+        <v>-0.4589</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8626</v>
+        <v>-0.8471</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0951</v>
+        <v>0.6352</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0907</v>
+        <v>-0.0258</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0044</v>
+        <v>0.6611</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8681</v>
+        <v>3.2634</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3064</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5617</v>
+        <v>2.396</v>
       </c>
       <c r="G4" t="n">
-        <v>2.529</v>
+        <v>4.1437</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2526</v>
+        <v>1.0454</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2763</v>
+        <v>3.0983</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7821</v>
+        <v>3.4391</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3321</v>
+        <v>1.1754</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4499</v>
+        <v>2.2638</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7469</v>
+        <v>0.7046</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0795</v>
+        <v>-0.13</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1389</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5243</v>
+        <v>-0.2954</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6145</v>
+        <v>-0.3573</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2478</v>
+        <v>3.0562</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9795</v>
+        <v>0.8254</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2683</v>
+        <v>2.2308</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2628</v>
+        <v>0.2492</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4707</v>
+        <v>0.4547</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2079</v>
+        <v>-0.2055</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4523</v>
+        <v>-0.4843</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1101</v>
+        <v>0.082</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5625</v>
+        <v>-0.5662</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7151</v>
+        <v>0.7335</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2365</v>
+        <v>0.0558</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1785</v>
+        <v>0.0624</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0581</v>
+        <v>-0.0066</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5526</v>
+        <v>2.2607</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3069</v>
+        <v>2.053</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2457</v>
+        <v>0.2078</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1447</v>
+        <v>2.516</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0447</v>
+        <v>0.2446</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>2.2714</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4614</v>
+        <v>1.7537</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1878</v>
+        <v>0.3168</v>
       </c>
       <c r="L6" t="n">
-        <v>2.2736</v>
+        <v>1.4369</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6833</v>
+        <v>0.7623</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1431</v>
+        <v>-0.0722</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3652</v>
+        <v>0.5367</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8861</v>
+        <v>0.2993</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4791</v>
+        <v>0.2374</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>J. COBBS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0299</v>
+        <v>2.2519</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8741</v>
+        <v>1.9204</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1558</v>
+        <v>0.3315</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2137</v>
+        <v>1.4152</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8227</v>
+        <v>0.2236</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0364</v>
+        <v>1.1916</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1826</v>
+        <v>0.7395</v>
       </c>
       <c r="K7" t="n">
-        <v>0.658</v>
+        <v>0.3825</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5246</v>
+        <v>0.357</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9689</v>
+        <v>0.6757</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4807</v>
+        <v>-0.1588</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5118</v>
+        <v>0.8345</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1357</v>
+        <v>-0.3031</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8257</v>
+        <v>-0.4533</v>
       </c>
       <c r="U7" t="n">
-        <v>0.31</v>
+        <v>0.1503</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5463</v>
+        <v>0.2292</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>K. PERRY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6462</v>
+        <v>2.1173</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6209</v>
+        <v>-1.0576</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2671</v>
+        <v>3.175</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2246</v>
+        <v>1.7585</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1979</v>
+        <v>-0.1985</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0267</v>
+        <v>1.9569</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5211</v>
+        <v>0.9248</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3534</v>
+        <v>0.4342</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1676</v>
+        <v>0.4906</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2965</v>
+        <v>0.8336</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1556</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1409</v>
+        <v>1.4663</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2683</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2368</v>
+        <v>-0.324</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0998</v>
+        <v>-0.2281</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.137</v>
+        <v>-0.0959</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. PERRY</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.534</v>
+        <v>1.4381</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3252</v>
+        <v>-1.6417</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8592</v>
+        <v>3.0798</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7635</v>
+        <v>-0.2219</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2035</v>
+        <v>-0.1873</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9671</v>
+        <v>-0.0346</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9547</v>
+        <v>-1.5437</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4431</v>
+        <v>-0.3587</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5116000000000001</v>
+        <v>-1.185</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8088</v>
+        <v>1.3219</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.1715</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4555</v>
+        <v>1.1504</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>2.2763</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.91</v>
+        <v>-0.4586</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5353</v>
+        <v>-0.098</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3747</v>
+        <v>-0.3606</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6105</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. COBBS</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1747</v>
+        <v>1.2937</v>
       </c>
       <c r="E10" t="n">
-        <v>1.285</v>
+        <v>1.2671</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1102</v>
+        <v>0.0266</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4105</v>
+        <v>1.2195</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2163</v>
+        <v>-0.8106</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1941</v>
+        <v>2.0301</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7589</v>
+        <v>2.1664</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3912</v>
+        <v>0.655</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3678</v>
+        <v>1.5114</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6515</v>
+        <v>-0.9469</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1749</v>
+        <v>-1.4656</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8264</v>
+        <v>0.5187</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.368</v>
+        <v>0.3913</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.113</v>
+        <v>0.2388</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.255</v>
+        <v>0.1524</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2249</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4141</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1046</v>
+        <v>-1.9217</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0646</v>
+        <v>-0.95</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.04</v>
+        <v>-0.9717</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.845</v>
+        <v>-0.8462</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.845</v>
+        <v>-0.8462</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1312,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1669</v>
+        <v>0.0139</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1113</v>
+        <v>0.1743</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0559</v>
+        <v>-2.6692</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7146</v>
+        <v>-2.3168</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3414</v>
+        <v>-0.3524</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8959</v>
+        <v>-2.9026</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1629</v>
+        <v>-2.1681</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.733</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6942</v>
+        <v>-2.7161</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2335</v>
+        <v>-1.2485</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2017</v>
+        <v>-0.1865</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8405</v>
+        <v>-0.4495</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.113</v>
+        <v>-0.6902</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2725</v>
+        <v>0.2407</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.2224</v>
+        <v>-5.0831</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.953</v>
+        <v>-3.8603</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2693</v>
+        <v>-1.2227</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.086</v>
+        <v>-1.0959</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.619</v>
+        <v>-1.6198</v>
       </c>
       <c r="I13" t="n">
-        <v>0.533</v>
+        <v>0.5239</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.3369</v>
+        <v>-1.354</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.5554</v>
+        <v>-1.562</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2185</v>
+        <v>0.2081</v>
       </c>
       <c r="M13" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1364</v>
+        <v>0.0128</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2114</v>
+        <v>0.2429</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.7466</v>
+        <v>18.0848</v>
       </c>
       <c r="E14" t="n">
-        <v>5.038</v>
+        <v>5.084999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>12.7088</v>
+        <v>13.0001</v>
       </c>
       <c r="G14" t="n">
-        <v>12.836</v>
+        <v>12.802</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.4634</v>
+        <v>-3.4474</v>
       </c>
       <c r="I14" t="n">
-        <v>16.2993</v>
+        <v>16.2494</v>
       </c>
       <c r="J14" t="n">
-        <v>8.520799999999999</v>
+        <v>8.269600000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4853000000000003</v>
+        <v>0.3658000000000003</v>
       </c>
       <c r="L14" t="n">
-        <v>8.035400000000001</v>
+        <v>7.904100000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>4.315099999999999</v>
+        <v>4.5325</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.9488</v>
+        <v>-3.8129</v>
       </c>
       <c r="O14" t="n">
-        <v>8.263800000000002</v>
+        <v>8.3454</v>
       </c>
       <c r="P14" t="n">
-        <v>6.8049</v>
+        <v>6.828900000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.9392</v>
+        <v>-7.967200000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5726</v>
+        <v>-1.2308</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.132</v>
+        <v>-1.7694</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5594</v>
+        <v>0.5387000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3213000000000001</v>
+        <v>-0.3153999999999997</v>
       </c>
       <c r="W14" t="n">
-        <v>6.5885</v>
+        <v>6.551700000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.9098</v>
+        <v>-6.8672</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3769</v>
+        <v>7.0411</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9872</v>
+        <v>5.9813</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3896</v>
+        <v>1.0598</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6487</v>
+        <v>6.6473</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2656</v>
+        <v>4.2515</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3831</v>
+        <v>2.3959</v>
       </c>
       <c r="J15" t="n">
-        <v>7.0525</v>
+        <v>7.0134</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1418</v>
+        <v>4.1089</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9107</v>
+        <v>2.9045</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4038</v>
+        <v>-0.366</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1238</v>
+        <v>0.1426</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5276</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3081</v>
+        <v>0.382</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1281</v>
+        <v>-0.0634</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.18</v>
+        <v>0.4454</v>
       </c>
       <c r="V15" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="W15" t="n">
-        <v>3.5994</v>
+        <v>3.584</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>A. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.353</v>
+        <v>-0.4093</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8447</v>
+        <v>0.1816</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5083</v>
+        <v>-0.5909</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0701</v>
+        <v>-0.6737</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8139</v>
+        <v>-0.6261</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7437</v>
+        <v>-0.0475</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.1594</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7552</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>0.5958</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5896</v>
+        <v>-0.5143</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0795</v>
+        <v>0.129</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6691</v>
+        <v>-0.6433</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8147</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0771</v>
+        <v>0.4041</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5194</v>
+        <v>0.0741</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5577</v>
+        <v>0.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1607</v>
+        <v>0.3155</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>1.405</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7534</v>
+        <v>-0.6539</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2739</v>
+        <v>-1.0564</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4795</v>
+        <v>0.4026</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.059</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6262</v>
+        <v>-0.8101</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0506</v>
+        <v>0.7511</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1547</v>
+        <v>-0.6635</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7517</v>
+        <v>-0.7379</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5971</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5222</v>
+        <v>0.6044</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1255</v>
+        <v>-0.0722</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.6766</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0556</v>
+        <v>1.0685</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3992</v>
+        <v>0.6361</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4549</v>
+        <v>0.4324</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3214</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4141</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9734</v>
+        <v>-1.4769</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0795</v>
+        <v>-1.5575</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1061</v>
+        <v>0.0805</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8085</v>
+        <v>-1.8102</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1587</v>
+        <v>0.1607</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9672</v>
+        <v>-1.9709</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5181</v>
+        <v>-1.5248</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2904</v>
+        <v>-0.2854</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6082</v>
+        <v>0.1057</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4386</v>
+        <v>-0.0327</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1697</v>
+        <v>0.1383</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4162</v>
+        <v>-1.6062</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1682</v>
+        <v>-0.1883</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.248</v>
+        <v>-1.4179</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9702</v>
+        <v>0.9738</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9275</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0453</v>
+        <v>0.0462</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7987</v>
+        <v>1.7879</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8285</v>
+        <v>-0.8141</v>
       </c>
       <c r="N19" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1615</v>
+        <v>-0.3507</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6079</v>
+        <v>-0.6088</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4464</v>
+        <v>0.2581</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0664</v>
+        <v>-2.0365</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0001</v>
+        <v>-1.1428</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9337</v>
+        <v>-0.8937</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.294</v>
+        <v>-0.1467</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0145</v>
+        <v>0.4593</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2795</v>
+        <v>-0.6061</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5181</v>
+        <v>0.1094</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0173</v>
+        <v>0.8618</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.5354</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2241</v>
+        <v>-0.2562</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0318</v>
+        <v>-0.4025</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2559</v>
+        <v>0.1463</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0919</v>
+        <v>0.1103</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3478</v>
+        <v>-0.1141</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2559</v>
+        <v>0.2243</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6804</v>
+        <v>-2.1398</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4861</v>
+        <v>-2.893</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1943</v>
+        <v>0.7532</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1545</v>
+        <v>-1.2943</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4559</v>
+        <v>-0.0116</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-1.2827</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1168</v>
+        <v>-1.5248</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8658</v>
+        <v>0.0172</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.749</v>
+        <v>-1.542</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2712</v>
+        <v>0.2305</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4099</v>
+        <v>-0.0289</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1387</v>
+        <v>0.2593</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5259</v>
+        <v>-0.1626</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4688</v>
+        <v>-0.2301</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0572</v>
+        <v>0.0675</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7503</v>
+        <v>-2.3379</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2987</v>
+        <v>-1.2091</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4516</v>
+        <v>-1.1288</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7324</v>
+        <v>-2.7224</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5309</v>
+        <v>-0.5395</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2016</v>
+        <v>-2.183</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4387</v>
+        <v>-0.4641</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5133</v>
+        <v>-0.5386</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2938</v>
+        <v>-2.2583</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0176</v>
+        <v>-0.0009</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.2762</v>
+        <v>-2.2574</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4035</v>
+        <v>-0.0024</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2722</v>
+        <v>-0.1516</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1313</v>
+        <v>0.1492</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8374</v>
+        <v>-3.1634</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0384</v>
+        <v>-1.3201</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.799</v>
+        <v>-1.8434</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3793</v>
+        <v>-3.3806</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3364</v>
+        <v>0.3252</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.7157</v>
+        <v>-3.7057</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7414</v>
+        <v>-1.7816</v>
       </c>
       <c r="K23" t="n">
-        <v>0.543</v>
+        <v>0.5129</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6379</v>
+        <v>-1.599</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2066</v>
+        <v>-0.1877</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4312</v>
+        <v>-1.4113</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>1.315</v>
+        <v>0.9895</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5837</v>
+        <v>0.3524</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7313</v>
+        <v>0.6371</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1831</v>
+        <v>-3.2876</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1856</v>
+        <v>-3.9335</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.6459</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1303</v>
+        <v>-3.537</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.14</v>
+        <v>-0.7007</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.9903</v>
+        <v>-2.8364</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.225</v>
+        <v>-3.2985</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0968</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.3218</v>
+        <v>-2.7566</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9053</v>
+        <v>-0.2386</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2368</v>
+        <v>-0.1588</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6685</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2005</v>
+        <v>0.2706</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0393</v>
+        <v>0.1389</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1612</v>
+        <v>0.1317</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1607</v>
+        <v>-0.9317</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. GARCIA</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8545</v>
+        <v>-3.3892</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7172</v>
+        <v>-2.3193</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1373</v>
+        <v>-1.07</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.6771</v>
+        <v>-4.1314</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1456</v>
+        <v>-0.1407</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.8228</v>
+        <v>-3.9907</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7664</v>
+        <v>-2.2423</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.0417</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.7247</v>
+        <v>-2.3317</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9107</v>
+        <v>-1.8891</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1874</v>
+        <v>-0.2301</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0981</v>
+        <v>-1.659</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7879</v>
+        <v>-0.0106</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8166</v>
+        <v>-0.077</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0287</v>
+        <v>0.0664</v>
       </c>
       <c r="V25" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.1578</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>D. GARCIA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.9614</v>
+        <v>-3.487</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.1322</v>
+        <v>-3.3851</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1707</v>
+        <v>-0.102</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.5318</v>
+        <v>-2.6678</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6984</v>
+        <v>0.1519</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.8335</v>
+        <v>-2.8197</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.2612</v>
+        <v>-1.7844</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5235</v>
+        <v>-0.0485</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.7377</v>
+        <v>-1.7359</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2707</v>
+        <v>-0.8835</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1749</v>
+        <v>0.2003</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0958</v>
+        <v>-1.0838</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.405</v>
+        <v>-0.4354</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0998</v>
+        <v>-0.4626</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3052</v>
+        <v>0.0272</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.1607</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-17.7466</v>
+        <v>-16.9466</v>
       </c>
       <c r="E27" t="n">
-        <v>-12.548</v>
+        <v>-12.8422</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.1988</v>
+        <v>-4.1047</v>
       </c>
       <c r="G27" t="n">
-        <v>-12.836</v>
+        <v>-12.802</v>
       </c>
       <c r="H27" t="n">
-        <v>3.463200000000001</v>
+        <v>3.4474</v>
       </c>
       <c r="I27" t="n">
-        <v>-16.2995</v>
+        <v>-16.2495</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.315399999999999</v>
+        <v>-4.5327</v>
       </c>
       <c r="K27" t="n">
-        <v>3.9486</v>
+        <v>3.812800000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-8.263900000000001</v>
+        <v>-8.345300000000002</v>
       </c>
       <c r="M27" t="n">
-        <v>-8.520799999999999</v>
+        <v>-8.269600000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.4853</v>
+        <v>-0.3654999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-8.035400000000001</v>
+        <v>-7.9041</v>
       </c>
       <c r="P27" t="n">
-        <v>-6.8051</v>
+        <v>-6.8291</v>
       </c>
       <c r="Q27" t="n">
-        <v>-14.7444</v>
+        <v>-14.7963</v>
       </c>
       <c r="R27" t="n">
-        <v>7.939100000000001</v>
+        <v>7.967099999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>1.5726</v>
+        <v>2.369</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.5594</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>2.1321</v>
+        <v>2.9076</v>
       </c>
       <c r="V27" t="n">
-        <v>0.3212999999999996</v>
+        <v>0.3155000000000004</v>
       </c>
       <c r="W27" t="n">
-        <v>7.070499999999999</v>
+        <v>7.025</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.7491</v>
+        <v>-6.7098</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104702_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104702_W28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.8672</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104702_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.7098</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
